--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/02_RedemptionCartPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/02_RedemptionCartPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43D23AD-A048-44C7-96EA-F5AFA258EC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9875F7FF-B80B-49F3-B245-D39DD96A5237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -321,10 +321,6 @@
 verify_redemptioncart_warningtoastmsg</t>
   </si>
   <si>
-    <t>redemptioncart_clickon_cancelbtn
-verifypagetitle</t>
-  </si>
-  <si>
     <t>Reward Catalogue</t>
   </si>
   <si>
@@ -335,14 +331,6 @@
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>catalogue_enter_qty
-hidekeyboard
-catalogue_clickon_submitbtn
-redemptioncart_clickon_checkoutbtn
-verifypagetitle
-navigatebacktodashboardpage</t>
   </si>
   <si>
     <t>06_REWARDCATALOGUE</t>
@@ -363,6 +351,20 @@
 catalogue_get_tdspercentage
 catalogue_clickon_submitbtn
 verify_redemptioncart_productcode</t>
+  </si>
+  <si>
+    <t>catalogue_enter_qty
+hidekeyboard
+catalogue_clickon_submitbtn
+redemptioncart_clickon_checkoutbtn
+redemptioncart_clickon_checkoutbtn
+verifypagetitle
+navigatebacktodashboardpage</t>
+  </si>
+  <si>
+    <t>redemptioncart_clickon_cancelbtn
+redemptioncart_clickon_cancelbtn
+verifypagetitle</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -1371,7 +1373,7 @@
         <v>39</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>44</v>
@@ -1393,7 +1395,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>23</v>
@@ -1420,7 +1422,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>24</v>
@@ -1447,7 +1449,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>25</v>
@@ -1474,7 +1476,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>26</v>
@@ -1501,7 +1503,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>27</v>
@@ -1528,7 +1530,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>28</v>
@@ -1555,7 +1557,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -1580,7 +1582,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
@@ -1607,7 +1609,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>31</v>
@@ -1634,7 +1636,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1663,7 +1665,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>33</v>
@@ -1690,7 +1692,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>34</v>
@@ -1717,7 +1719,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>35</v>
@@ -1739,39 +1741,39 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="87" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>37</v>
@@ -1780,16 +1782,16 @@
         <v>38</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>5</v>

--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/02_RedemptionCartPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/02_RedemptionCartPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9875F7FF-B80B-49F3-B245-D39DD96A5237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9F5059-F9AE-46D4-A611-28765F34A74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -362,7 +362,7 @@
 navigatebacktodashboardpage</t>
   </si>
   <si>
-    <t>redemptioncart_clickon_cancelbtn
+    <t>waitforsnackbardisappear
 redemptioncart_clickon_cancelbtn
 verifypagetitle</t>
   </si>

--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/02_RedemptionCartPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/02_RedemptionCartPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9F5059-F9AE-46D4-A611-28765F34A74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F819ED1-C220-47E2-ABDD-E1858C3B3693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="80">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -365,6 +365,9 @@
     <t>waitforsnackbardisappear
 redemptioncart_clickon_cancelbtn
 verifypagetitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -1310,7 +1313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
@@ -1768,7 +1771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
@@ -1795,6 +1798,9 @@
       </c>
       <c r="K17" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
